--- a/My project/JsonConverter/ExcelFiles/Dish.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Dish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCEBD84-331C-447C-8B15-91601243E974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011A9557-95A0-4C20-A57F-BD693CB1D711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="3600" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>(name)</t>
   </si>
@@ -82,6 +82,14 @@
   </si>
   <si>
     <t>CostType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -236,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -309,6 +317,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -562,6 +576,9 @@
       <c r="E2" s="13" t="s">
         <v>6</v>
       </c>
+      <c r="F2" s="30" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -579,6 +596,9 @@
       <c r="E3" s="17" t="s">
         <v>14</v>
       </c>
+      <c r="F3" s="31" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -596,7 +616,9 @@
       <c r="E4" s="29">
         <v>2</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -623,7 +645,9 @@
       <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3">
+        <v>150</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>

--- a/My project/JsonConverter/ExcelFiles/Dish.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Dish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011A9557-95A0-4C20-A57F-BD693CB1D711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACC95D6-46B1-490D-A1F3-EC7931056B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>(name)</t>
   </si>
@@ -73,15 +73,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Potato</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>CostCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -91,6 +83,21 @@
   <si>
     <t>Price</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostItemID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crop_Potato</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PriceItemID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dokkaebi_Coin</t>
   </si>
 </sst>
 </file>
@@ -244,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -319,10 +326,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -551,6 +555,8 @@
     <col min="3" max="3" width="50.7109375" style="28" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" style="12" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -576,8 +582,11 @@
       <c r="E2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="30" t="s">
-        <v>16</v>
+      <c r="F2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
@@ -591,13 +600,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -611,15 +623,17 @@
         <v>12</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" s="29">
         <v>2</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="15">
         <v>50</v>
       </c>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -640,15 +654,17 @@
         <v>11</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="15">
         <v>150</v>
       </c>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -664,8 +680,8 @@
       <c r="C6" s="21"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -681,8 +697,8 @@
       <c r="C7" s="20"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -698,8 +714,8 @@
       <c r="C8" s="22"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -715,8 +731,8 @@
       <c r="C9" s="22"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -732,8 +748,8 @@
       <c r="C10" s="23"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -749,8 +765,8 @@
       <c r="C11" s="23"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -766,8 +782,8 @@
       <c r="C12" s="22"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -783,8 +799,8 @@
       <c r="C13" s="20"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -800,8 +816,8 @@
       <c r="C14" s="23"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -817,8 +833,8 @@
       <c r="C15" s="23"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>

--- a/My project/JsonConverter/ExcelFiles/Dish.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Dish.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACC95D6-46B1-490D-A1F3-EC7931056B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C42352F-4D5D-4E62-B70D-5310ABFBEC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -324,9 +324,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -585,7 +582,7 @@
       <c r="F2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -632,7 +629,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -663,7 +660,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
